--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43182</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43182</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43182</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>-0.02599037321445527</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>244817</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>-0.02599037321445527</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>244817</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5904,7 +5904,7 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>43182</v>
+        <v>43185</v>
       </c>
       <c r="K64" t="n">
         <v>16</v>
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9157</v>
+        <v>9158</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2735,20 +2735,20 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>10983</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="K57" t="n">
-        <v>164</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E58" t="n">
         <v>5</v>
@@ -2809,11 +2809,11 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10983</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2837,16 +2837,16 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="K59" t="n">
-        <v>15</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2877,13 +2877,13 @@
         <v>453</v>
       </c>
       <c r="K60" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         <v>453</v>
       </c>
       <c r="K61" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         <v>453</v>
       </c>
       <c r="K62" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2988,13 +2988,13 @@
         <v>453</v>
       </c>
       <c r="K63" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>308</v>
+        <v>453</v>
       </c>
       <c r="K64" t="n">
-        <v>147</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
@@ -3068,7 +3068,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>453</v>
+        <v>308</v>
       </c>
       <c r="K66" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3136,13 +3136,13 @@
         <v>453</v>
       </c>
       <c r="K67" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3173,13 +3173,13 @@
         <v>453</v>
       </c>
       <c r="K68" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>453</v>
       </c>
       <c r="K69" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3247,13 +3247,13 @@
         <v>453</v>
       </c>
       <c r="K70" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3284,13 +3284,13 @@
         <v>453</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>453</v>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>453</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>453</v>
       </c>
       <c r="K74" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>453</v>
       </c>
       <c r="K75" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3469,28 +3469,65 @@
         <v>453</v>
       </c>
       <c r="K76" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>10983</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>453</v>
+      </c>
+      <c r="K77" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3506,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6209,60 +6246,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>374658</v>
+        <v>400054</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.08898636852164356</v>
+        <v>-0.02723377766538441</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J73" t="n">
-        <v>31236</v>
+        <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>8103</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>398039</v>
+        <v>374658</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.06240624783135553</v>
+        <v>-0.06348143000694906</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>168210</v>
+        <v>272555</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6271,13 +6308,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.3828401607015098</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J74" t="n">
-        <v>26868</v>
+        <v>31236</v>
       </c>
       <c r="K74" t="n">
-        <v>12404</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="75">
@@ -6293,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.06240624783135553</v>
       </c>
       <c r="E75" t="n">
         <v>5</v>
@@ -6308,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>-0.3828401607015098</v>
       </c>
       <c r="J75" t="n">
         <v>26868</v>
@@ -6320,23 +6357,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>244817</v>
+        <v>168210</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6345,32 +6382,32 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.4554247666607217</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>39517</v>
+        <v>26868</v>
       </c>
       <c r="K76" t="n">
-        <v>72</v>
+        <v>12404</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
         <v>244817</v>
@@ -6382,32 +6419,32 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>0.4554247666607217</v>
       </c>
       <c r="J77" t="n">
-        <v>40235</v>
+        <v>39517</v>
       </c>
       <c r="K77" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
         <v>244817</v>
@@ -6422,29 +6459,29 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>40741</v>
+        <v>40235</v>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>244817</v>
@@ -6459,26 +6496,26 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>41352</v>
+        <v>40741</v>
       </c>
       <c r="K79" t="n">
-        <v>296</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>411319</v>
+        <v>400317</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.02748321954850781</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E80" t="n">
         <v>4</v>
@@ -6496,32 +6533,32 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>41345</v>
+        <v>41352</v>
       </c>
       <c r="K80" t="n">
-        <v>1247</v>
+        <v>296</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>395094</v>
+        <v>411319</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>0.02748321954850781</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -6530,35 +6567,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>26611</v>
+        <v>41345</v>
       </c>
       <c r="K81" t="n">
-        <v>13235</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>398039</v>
+        <v>395094</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.007453922357717404</v>
+        <v>-0.03944626919738695</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -6567,13 +6604,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1133009554075085</v>
       </c>
       <c r="J82" t="n">
-        <v>29399</v>
+        <v>26611</v>
       </c>
       <c r="K82" t="n">
-        <v>9655</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="83">
@@ -6589,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.007453922357717404</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
@@ -6604,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J83" t="n">
         <v>29399</v>
@@ -6616,20 +6653,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F84" t="n">
         <v>244817</v>
@@ -6644,29 +6681,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>39659</v>
+        <v>29399</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>9655</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>244817</v>
@@ -6681,29 +6718,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>40235</v>
+        <v>39659</v>
       </c>
       <c r="K85" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F86" t="n">
         <v>244817</v>
@@ -6718,29 +6755,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>40758</v>
+        <v>40235</v>
       </c>
       <c r="K86" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>244817</v>
@@ -6755,29 +6792,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>41352</v>
+        <v>40758</v>
       </c>
       <c r="K87" t="n">
-        <v>405</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>411319</v>
+        <v>400317</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02748321954850781</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>244817</v>
@@ -6786,75 +6823,75 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.0002940972236405152</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>41344</v>
+        <v>41352</v>
       </c>
       <c r="K88" t="n">
-        <v>1355</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>395094</v>
+        <v>411319</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>0.02748321954850781</v>
       </c>
       <c r="E89" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1129736329520722</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J89" t="n">
-        <v>26611</v>
+        <v>41344</v>
       </c>
       <c r="K89" t="n">
-        <v>13235</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>398164</v>
+        <v>395094</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.007770302763393015</v>
+        <v>-0.03944626919738695</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F90" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -6863,32 +6900,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J90" t="n">
-        <v>32472</v>
+        <v>26611</v>
       </c>
       <c r="K90" t="n">
-        <v>6659</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>402212</v>
+        <v>398164</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01016666499231472</v>
+        <v>0.007770302763393015</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>244817</v>
@@ -6900,32 +6937,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J91" t="n">
-        <v>39697</v>
+        <v>32472</v>
       </c>
       <c r="K91" t="n">
-        <v>19</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01016666499231472</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>244817</v>
@@ -6940,29 +6977,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>40232</v>
+        <v>39697</v>
       </c>
       <c r="K92" t="n">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>244817</v>
@@ -6977,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>40759</v>
+        <v>40232</v>
       </c>
       <c r="K93" t="n">
         <v>137</v>
@@ -6986,23 +7023,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>245147</v>
+        <v>244817</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -7011,71 +7048,108 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.001347945608352361</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>41352</v>
+        <v>40759</v>
       </c>
       <c r="K94" t="n">
-        <v>472</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>400317</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.0005498666573355961</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>245147</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.001347945608352361</v>
+      </c>
+      <c r="J95" t="n">
+        <v>41352</v>
+      </c>
+      <c r="K95" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>411319</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.02748321954850781</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>2</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>244817</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>72</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>-0.001052429766629818</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>41340</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>1427</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>16225</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>-27738</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>14729</v>
       </c>
     </row>
@@ -7091,7 +7165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9794,23 +9868,23 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>31012</v>
+        <v>50942</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -9819,19 +9893,19 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.3912292410977189</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>7777</v>
+        <v>9158</v>
       </c>
       <c r="K73" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -9841,13 +9915,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>26198</v>
+        <v>31012</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -9856,13 +9930,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.1552302334580163</v>
+        <v>-0.3912292410977189</v>
       </c>
       <c r="J74" t="n">
-        <v>7346</v>
+        <v>7777</v>
       </c>
       <c r="K74" t="n">
-        <v>1310</v>
+        <v>937</v>
       </c>
     </row>
     <row r="75">
@@ -9893,7 +9967,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>-0.1552302334580163</v>
       </c>
       <c r="J75" t="n">
         <v>7346</v>
@@ -9905,23 +9979,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -9930,19 +10004,19 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>8234</v>
+        <v>7346</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -9952,10 +10026,10 @@
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
         <v>50942</v>
@@ -9967,32 +10041,32 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J77" t="n">
-        <v>8382</v>
+        <v>8234</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
         <v>50942</v>
@@ -10007,16 +10081,16 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>8513</v>
+        <v>8382</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -10026,10 +10100,10 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>50942</v>
@@ -10044,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>8808</v>
+        <v>8513</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -10053,7 +10127,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -10081,7 +10155,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>9007</v>
+        <v>8808</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -10090,23 +10164,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -10115,19 +10189,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>7708</v>
+        <v>9007</v>
       </c>
       <c r="K81" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -10137,13 +10211,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10152,13 +10226,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J82" t="n">
-        <v>8068</v>
+        <v>7708</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="83">
@@ -10189,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J83" t="n">
         <v>8068</v>
@@ -10201,20 +10275,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F84" t="n">
         <v>50942</v>
@@ -10229,16 +10303,16 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>8243</v>
+        <v>8068</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -10248,10 +10322,10 @@
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>50942</v>
@@ -10266,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>8396</v>
+        <v>8243</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -10275,20 +10349,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F86" t="n">
         <v>50942</v>
@@ -10303,16 +10377,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>8539</v>
+        <v>8396</v>
       </c>
       <c r="K86" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -10322,10 +10396,10 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>50942</v>
@@ -10340,16 +10414,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>8824</v>
+        <v>8539</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -10362,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>50942</v>
@@ -10377,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>9019</v>
+        <v>8824</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -10386,23 +10460,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -10411,19 +10485,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>7708</v>
+        <v>9019</v>
       </c>
       <c r="K89" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -10433,13 +10507,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F90" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -10448,32 +10522,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J90" t="n">
-        <v>8082</v>
+        <v>7708</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>50942</v>
@@ -10485,19 +10559,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J91" t="n">
-        <v>8259</v>
+        <v>8082</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -10507,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>50942</v>
@@ -10525,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>8417</v>
+        <v>8259</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -10534,20 +10608,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>50942</v>
@@ -10562,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>8578</v>
+        <v>8417</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -10571,7 +10645,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -10581,10 +10655,10 @@
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>50942</v>
@@ -10599,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>8836</v>
+        <v>8578</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -10608,7 +10682,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -10621,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
         <v>50942</v>
@@ -10636,31 +10710,68 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
+        <v>8836</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>88522</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>50942</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>9022</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>-256</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>24744</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>1314</v>
       </c>
     </row>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2766,7 +2766,7 @@
         <v>453</v>
       </c>
       <c r="K57" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6274,10 +6274,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J73" t="n">
-        <v>43185</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2766,7 +2766,7 @@
         <v>453</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
@@ -6274,10 +6274,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6250,13 +6250,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>400054</v>
+        <v>403155</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.02723377766538441</v>
+        <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.06348143000694906</v>
+        <v>-0.07068497228113256</v>
       </c>
       <c r="E74" t="n">
         <v>9</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>244817</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>244817</v>
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9158</v>
+        <v>9159</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>244817</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>50942</v>
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9159</v>
+        <v>9161</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9161</v>
+        <v>9164</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9164</v>
+        <v>9167</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>244817</v>
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>50942</v>
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9167</v>
+        <v>9169</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6277,7 +6277,7 @@
         <v>43185</v>
       </c>
       <c r="K73" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>-0.0196934254742811</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>244817</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3031,7 +3031,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3059,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>308</v>
+        <v>453</v>
       </c>
       <c r="K65" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66">
@@ -3105,7 +3105,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>453</v>
+        <v>308</v>
       </c>
       <c r="K67" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3173,13 +3173,13 @@
         <v>453</v>
       </c>
       <c r="K68" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>453</v>
       </c>
       <c r="K69" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3247,13 +3247,13 @@
         <v>453</v>
       </c>
       <c r="K70" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3284,13 +3284,13 @@
         <v>453</v>
       </c>
       <c r="K71" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>453</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>453</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>453</v>
       </c>
       <c r="K74" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>453</v>
       </c>
       <c r="K75" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3469,13 +3469,13 @@
         <v>453</v>
       </c>
       <c r="K76" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3506,28 +3506,65 @@
         <v>453</v>
       </c>
       <c r="K77" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>10983</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>453</v>
+      </c>
+      <c r="K78" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3543,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6579,60 +6616,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>395094</v>
+        <v>403155</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>-0.01984834155485159</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>26611</v>
+        <v>43185</v>
       </c>
       <c r="K82" t="n">
-        <v>13235</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>398039</v>
+        <v>395094</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.007453922357717404</v>
+        <v>-0.01999479108531458</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -6641,13 +6678,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J83" t="n">
-        <v>29399</v>
+        <v>26611</v>
       </c>
       <c r="K83" t="n">
-        <v>9655</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="84">
@@ -6663,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.007453922357717404</v>
       </c>
       <c r="E84" t="n">
         <v>8</v>
@@ -6678,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J84" t="n">
         <v>29399</v>
@@ -6690,20 +6727,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F85" t="n">
         <v>244817</v>
@@ -6718,29 +6755,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>39659</v>
+        <v>29399</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>9655</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>244817</v>
@@ -6755,29 +6792,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>40235</v>
+        <v>39659</v>
       </c>
       <c r="K86" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
         <v>244817</v>
@@ -6792,29 +6829,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>40758</v>
+        <v>40235</v>
       </c>
       <c r="K87" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
         <v>244817</v>
@@ -6829,29 +6866,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>41352</v>
+        <v>40758</v>
       </c>
       <c r="K88" t="n">
-        <v>405</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>411319</v>
+        <v>400317</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.02748321954850781</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>244817</v>
@@ -6860,75 +6897,75 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0002940972236405152</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>41344</v>
+        <v>41352</v>
       </c>
       <c r="K89" t="n">
-        <v>1355</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>395094</v>
+        <v>411319</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>0.02748321954850781</v>
       </c>
       <c r="E90" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.1129736329520722</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J90" t="n">
-        <v>26611</v>
+        <v>41344</v>
       </c>
       <c r="K90" t="n">
-        <v>13235</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>398164</v>
+        <v>395094</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.007770302763393015</v>
+        <v>-0.03944626919738695</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -6937,32 +6974,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J91" t="n">
-        <v>32472</v>
+        <v>26611</v>
       </c>
       <c r="K91" t="n">
-        <v>6659</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>402212</v>
+        <v>398164</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01016666499231472</v>
+        <v>0.007770302763393015</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>244817</v>
@@ -6974,32 +7011,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J92" t="n">
-        <v>39697</v>
+        <v>32472</v>
       </c>
       <c r="K92" t="n">
-        <v>19</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01016666499231472</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>244817</v>
@@ -7014,29 +7051,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>40232</v>
+        <v>39697</v>
       </c>
       <c r="K93" t="n">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>244817</v>
@@ -7051,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>40759</v>
+        <v>40232</v>
       </c>
       <c r="K94" t="n">
         <v>137</v>
@@ -7060,23 +7097,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>245147</v>
+        <v>244817</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -7085,71 +7122,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.001347945608352361</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>41352</v>
+        <v>40759</v>
       </c>
       <c r="K95" t="n">
-        <v>472</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>400317</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.0005498666573355961</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>245147</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.001347945608352361</v>
+      </c>
+      <c r="J96" t="n">
+        <v>41352</v>
+      </c>
+      <c r="K96" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>411319</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.02748321954850781</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>2</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>244817</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>72</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>-0.001052429766629818</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>41340</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>1427</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>16225</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>-27738</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>14729</v>
       </c>
     </row>
@@ -7165,7 +7239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10201,23 +10275,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10226,19 +10300,19 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>7708</v>
+        <v>9167</v>
       </c>
       <c r="K82" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -10248,13 +10322,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -10263,13 +10337,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J83" t="n">
-        <v>8068</v>
+        <v>7708</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="84">
@@ -10300,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J84" t="n">
         <v>8068</v>
@@ -10312,20 +10386,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F85" t="n">
         <v>50942</v>
@@ -10340,16 +10414,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>8243</v>
+        <v>8068</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -10359,10 +10433,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>50942</v>
@@ -10377,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>8396</v>
+        <v>8243</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -10386,20 +10460,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
         <v>50942</v>
@@ -10414,16 +10488,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>8539</v>
+        <v>8396</v>
       </c>
       <c r="K87" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -10433,10 +10507,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
         <v>50942</v>
@@ -10451,16 +10525,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>8824</v>
+        <v>8539</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -10473,7 +10547,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>50942</v>
@@ -10488,7 +10562,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>9019</v>
+        <v>8824</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -10497,23 +10571,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -10522,19 +10596,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>7708</v>
+        <v>9019</v>
       </c>
       <c r="K90" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -10544,13 +10618,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -10559,32 +10633,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J91" t="n">
-        <v>8082</v>
+        <v>7708</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>50942</v>
@@ -10596,19 +10670,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J92" t="n">
-        <v>8259</v>
+        <v>8082</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -10618,10 +10692,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>50942</v>
@@ -10636,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>8417</v>
+        <v>8259</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -10645,20 +10719,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>50942</v>
@@ -10673,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>8578</v>
+        <v>8417</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -10682,7 +10756,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -10692,10 +10766,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>50942</v>
@@ -10710,7 +10784,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>8836</v>
+        <v>8578</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -10719,7 +10793,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -10732,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
         <v>50942</v>
@@ -10747,31 +10821,68 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>8836</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>88522</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>50942</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>9022</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>-256</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>24744</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>1314</v>
       </c>
     </row>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43185</v>
       </c>
       <c r="K82" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>403155</v>
+        <v>404022</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.01984834155485159</v>
+        <v>-0.01774048852593729</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.01999479108531458</v>
+        <v>-0.02209780655508858</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>404022</v>
+        <v>403872</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.01774048852593729</v>
+        <v>-0.01810516898076675</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         <v>43185</v>
       </c>
       <c r="K82" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83">
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.02209780655508858</v>
+        <v>-0.02173460898502496</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6644,10 +6644,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43185</v>
+        <v>43218</v>
       </c>
       <c r="K82" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -10303,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>9167</v>
+        <v>9168</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43218</v>
       </c>
       <c r="K82" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43218</v>
       </c>
       <c r="K82" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
@@ -10306,7 +10306,7 @@
         <v>9168</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6644,10 +6644,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43218</v>
+        <v>43240</v>
       </c>
       <c r="K82" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>9168</v>
+        <v>9172</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43240</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83">
@@ -10303,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>9172</v>
+        <v>9181</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6644,10 +6644,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43240</v>
+        <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>-0.01810516898076675</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>244817</v>
@@ -6647,7 +6647,7 @@
         <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
@@ -10306,7 +10306,7 @@
         <v>9181</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>9181</v>
+        <v>9184</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>-0.01810516898076675</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>244817</v>
@@ -6647,7 +6647,7 @@
         <v>43259</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -3062,7 +3062,7 @@
         <v>453</v>
       </c>
       <c r="K65" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66">
@@ -6644,10 +6644,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43259</v>
+        <v>43278</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
@@ -10291,7 +10291,7 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>50942</v>
+        <v>43661</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10300,13 +10300,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>-0.1429272505987201</v>
       </c>
       <c r="J82" t="n">
         <v>9184</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>-0.399967934770161</v>
       </c>
       <c r="J83" t="n">
         <v>7708</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6647,7 +6647,7 @@
         <v>43278</v>
       </c>
       <c r="K82" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -10303,10 +10303,10 @@
         <v>-0.1429272505987201</v>
       </c>
       <c r="J82" t="n">
-        <v>9184</v>
+        <v>9187</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6644,10 +6644,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43278</v>
+        <v>43312</v>
       </c>
       <c r="K82" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -6644,7 +6644,7 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J82" t="n">
-        <v>43312</v>
+        <v>43305</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -10303,7 +10303,7 @@
         <v>-0.1429272505987201</v>
       </c>
       <c r="J82" t="n">
-        <v>9187</v>
+        <v>9186</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
